--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/Datatypes.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/1-Data-Model/Datatypes.xlsx
@@ -1919,8 +1919,8 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="B83:I83"/>
     <mergeCell ref="B102:N102"/>
@@ -1946,7 +1946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L62"/>
+  <dimension ref="B2:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2262,176 +2262,182 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Method Customer NewCustomer(String name, String city)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Customer NewCustomer(String name, String city)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>return new Customer(name = name, address = new Address(city = city));</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>= new Customer(name = name, address = new Address(city = city))</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Test NewCustomer NewCustomerTest</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="10" t="inlineStr">
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>_res_.name</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>_res_.country</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>_res_.address.city</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>_res_.address.zipCode</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Zip Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Ann</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Ann</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>00000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Ann</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Denver</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>00000</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Datatype Resident</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+      <c r="C40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="7" t="inlineStr">
@@ -2441,385 +2447,398 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
           <t>city</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult NamedArguments(String name, String city)</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="8" t="inlineStr">
+      <c r="C44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>AnyOrder</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>= new Address(city = city, street = name)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Swapped</t>
+          <t>AnyOrder</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>= Customer(name = city, address = Address(city = name))</t>
+          <t>= new Address(city = city, street = name)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>AnyOrderCity</t>
+          <t>Swapped</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>= $AnyOrder.city</t>
+          <t>= Customer(name = city, address = Address(city = name))</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>AnyOrderStreet</t>
+          <t>AnyOrderCity</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>= $AnyOrder.street</t>
+          <t>= $AnyOrder.city</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SwappedName</t>
+          <t>AnyOrderStreet</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>= $Swapped.name</t>
+          <t>= $AnyOrder.street</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SwappedCity</t>
+          <t>SwappedName</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>= $Swapped.address.city</t>
+          <t>= $Swapped.name</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>StreetFromCity</t>
+          <t>SwappedCity</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>= new Address(street = city).street</t>
+          <t>= $Swapped.address.city</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>TwoFieldsSwapped</t>
+          <t>StreetFromCity</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>= new Resident(name = city, city = name)</t>
+          <t>= new Address(street = city).street</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>TwoFieldsReordered</t>
+          <t>TwoFieldsSwapped</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>= new Resident(city = city, name = name)</t>
+          <t>= new Resident(name = city, city = name)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>SwappedResident</t>
+          <t>TwoFieldsReordered</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>= $TwoFieldsSwapped.name + " in " + $TwoFieldsSwapped.city</t>
+          <t>= new Resident(city = city, name = name)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>ReorderedResident</t>
+          <t>SwappedResident</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>= $TwoFieldsReordered.name + " in " + $TwoFieldsReordered.city</t>
+          <t>= $TwoFieldsSwapped.name + " in " + $TwoFieldsSwapped.city</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>NameAfter</t>
+          <t>ReorderedResident</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>= name</t>
+          <t>= $TwoFieldsReordered.name + " in " + $TwoFieldsReordered.city</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="inlineStr">
         <is>
+          <t>NameAfter</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>= name</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="inlineStr">
+        <is>
           <t>CityAfter</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>= city</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Test NamedArguments NamedArgumentsTest</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="5" t="n"/>
-      <c r="K59" s="5" t="n"/>
-      <c r="L59" s="6" t="n"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="10" t="inlineStr">
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>_res_.$AnyOrderCity</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>_res_.$AnyOrderStreet</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>_res_.$SwappedName</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>_res_.$SwappedCity</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>_res_.$StreetFromCity</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>_res_.$SwappedResident</t>
         </is>
       </c>
-      <c r="J60" s="10" t="inlineStr">
+      <c r="J61" s="10" t="inlineStr">
         <is>
           <t>_res_.$ReorderedResident</t>
         </is>
       </c>
-      <c r="K60" s="10" t="inlineStr">
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t>_res_.$NameAfter</t>
         </is>
       </c>
-      <c r="L60" s="10" t="inlineStr">
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>_res_.$CityAfter</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Any Order City</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Any Order Street</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Swapped Name</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Swapped City</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>Street From City</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>Swapped Resident</t>
         </is>
       </c>
-      <c r="J61" s="8" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>Reordered Resident</t>
         </is>
       </c>
-      <c r="K61" s="8" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>Name After</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
+      <c r="L62" s="8" t="inlineStr">
         <is>
           <t>City After</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="7" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="H62" s="11" t="inlineStr">
+      <c r="H63" s="11" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>Boston in Ann</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J63" s="11" t="inlineStr">
         <is>
           <t>Ann in Boston</t>
         </is>
       </c>
-      <c r="K62" s="11" t="inlineStr">
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="L62" s="11" t="inlineStr">
+      <c r="L63" s="11" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B33:G33"/>
+  <mergeCells count="10">
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B59:L59"/>
     <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B60:L60"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2832,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I24"/>
+  <dimension ref="B2:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2896,177 +2915,196 @@
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Method String Describe(Customer customer)</t>
-        </is>
-      </c>
+          <t>Spreadsheet String Describe(Customer customer)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>return customer.name + " from " + customer.country;</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>= customer.name + " from " + customer.country</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult InheritanceExample()</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+      <c r="C14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>= new PremiumCustomer(name = "Bob", manager = "Ann")</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>InheritedDefault</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>= $Premium.country</t>
+          <t>= new PremiumCustomer(name = "Bob", manager = "Ann")</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OwnDefault</t>
+          <t>InheritedDefault</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>= $Premium.discount</t>
+          <t>= $Premium.country</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>OwnDefault</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>= $Premium.manager</t>
+          <t>= $Premium.discount</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>= $Premium.manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>AsParent</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>= Describe($Premium)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Test InheritanceExample InheritanceExampleTest</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$InheritedDefault</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$OwnDefault</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$Manager</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$AsParent</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Inherited Default</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Own Default</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>As Parent</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C25" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Ann</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Bob from USA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="5">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B22:E22"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B10:C10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3079,7 +3117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I101"/>
+  <dimension ref="B2:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -3353,633 +3391,652 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Method CustomerTier ToTier(String tierName)</t>
-        </is>
-      </c>
+          <t>Spreadsheet CustomerTier ToTier(String tierName)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>return (CustomerTier) tierName;</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>= (CustomerTier) tierName</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Test ToTier ToTierTest</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="10" t="inlineStr">
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>tierName</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>_error_</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="8" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Tier Name</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="7" t="inlineStr">
         <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="C51" s="11" t="n"/>
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Object 'Platinum' is outside of valid domain 'CustomerTier'. Valid values: [Bronze, Silver, Gold]</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1">
-      <c r="B52" s="2" t="inlineStr">
+    <row r="53" ht="16.5" customHeight="1">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>"getValues(Type)" returns all values of a vocabulary as an array, in the order of the table.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="4" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult VocabularyValues()</t>
         </is>
       </c>
-      <c r="C54" s="6" t="n"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="8" t="inlineStr">
+      <c r="C55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>AllTiers</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>= getValues(CustomerTier)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>TierCount</t>
+          <t>AllTiers</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>= length($AllTiers)</t>
+          <t>= getValues(CustomerTier)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>BestRating</t>
+          <t>TierCount</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>= max(getValues(StarRating))</t>
+          <t>= length($AllTiers)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>DefaultTier</t>
+          <t>BestRating</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>= new Membership().tier</t>
+          <t>= max(getValues(StarRating))</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>DefaultTier</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>= new Membership().tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="7" t="inlineStr">
+        <is>
           <t>DefaultRating</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>= new Membership().rating</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="4" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Test VocabularyValues VocabularyValuesTest</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="6" t="n"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="10" t="inlineStr">
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$AllTiers</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$TierCount</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$BestRating</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$DefaultTier</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>_res_.$Value$DefaultRating</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>All Tiers</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Tier Count</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>Best Rating</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Default Tier</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>Default Rating</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="11" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>Bronze, Silver, Gold</t>
         </is>
       </c>
-      <c r="C65" s="11" t="n">
+      <c r="C66" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D66" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F65" s="11" t="n">
+      <c r="F66" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Arrays of vocabulary values</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1">
-      <c r="B69" s="2" t="inlineStr">
+    <row r="70" ht="16.5" customHeight="1">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>A field, a parameter or a return value can be an array of a vocabulary type, written as a comma-separated list. A rule that returns an array accepts a single value in a cell. "sort" orders vocabulary values as text, not in the order of the vocabulary table.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="4" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Datatype TierHistory</t>
         </is>
       </c>
-      <c r="C71" s="6" t="n"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>member</t>
-        </is>
-      </c>
+      <c r="C72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="7" t="inlineStr">
         <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="7" t="inlineStr">
+        <is>
           <t>CustomerTier[]</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>tiers</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="4" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Data TierHistory tierHistories</t>
         </is>
       </c>
-      <c r="C75" s="6" t="n"/>
-    </row>
-    <row r="76">
-      <c r="B76" s="10" t="inlineStr">
+      <c r="C76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>member</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>tiers</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="8" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Ann</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Silver, Bronze</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Bronze</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="7" t="inlineStr">
         <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="7" t="inlineStr">
+        <is>
           <t>Carl</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>Silver, Gold</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="4" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>SmartRules CustomerTier[] HigherTiers(CustomerTier tier)</t>
         </is>
       </c>
-      <c r="C82" s="6" t="n"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="8" t="inlineStr">
+      <c r="C83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Customer Tier</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Higher Tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t>Silver, Gold</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="7" t="inlineStr">
         <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Silver, Gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="7" t="inlineStr">
+        <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="4" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Spreadsheet SpreadsheetResult TierSummary(TierHistory[] histories)</t>
         </is>
       </c>
-      <c r="C87" s="6" t="n"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="8" t="inlineStr">
+      <c r="C88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>AllTiers</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>= flatten(tiers(histories))</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>SortedTiers</t>
+          <t>AllTiers</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>= sort($AllTiers)</t>
+          <t>= flatten(tiers(histories))</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>AboveSilver</t>
+          <t>SortedTiers</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>= HigherTiers("Silver")</t>
+          <t>= sort($AllTiers)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="7" t="inlineStr">
         <is>
+          <t>AboveSilver</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>= HigherTiers("Silver")</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="7" t="inlineStr">
+        <is>
           <t>AboveGold</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>= HigherTiers("Gold")</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16.5" customHeight="1">
-      <c r="B94" s="2" t="inlineStr">
+    <row r="95" ht="16.5" customHeight="1">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>In a test, a parameter that is an array of objects takes the keys of several rows of a data table, separated by commas.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="4" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Test TierSummary TierSummaryTest</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="6" t="n"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>histories</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>_res_.$AllTiers</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>_res_.$SortedTiers</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>_res_.$AboveSilver</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>_res_.$AboveGold</t>
-        </is>
-      </c>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="B98" s="10" t="inlineStr">
         <is>
+          <t>histories</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>_res_.$AllTiers</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>_res_.$SortedTiers</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>_res_.$AboveSilver</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>_res_.$AboveGold</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="10" t="inlineStr">
+        <is>
           <t>&gt;tierHistories</t>
         </is>
       </c>
-      <c r="C98" s="10" t="n"/>
-      <c r="D98" s="10" t="n"/>
-      <c r="E98" s="10" t="n"/>
-      <c r="F98" s="10" t="n"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="8" t="inlineStr">
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Members</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>All Tiers</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Sorted Tiers</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>Above Silver</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>Above Gold</t>
         </is>
       </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Ann, Carl</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>Silver, Bronze, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>Bronze, Gold, Silver, Silver</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="7" t="inlineStr">
         <is>
+          <t>Ann, Carl</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Silver, Bronze, Silver, Gold</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Bronze, Gold, Silver, Silver</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="7" t="inlineStr">
+        <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="C101" s="11" t="inlineStr">
+      <c r="C102" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F101" s="11" t="n"/>
+      <c r="F102" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B52:I52"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B70:I70"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B97:F97"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
